--- a/bench/data/files/synthetic5_A.xlsx
+++ b/bench/data/files/synthetic5_A.xlsx
@@ -549,55 +549,51 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Junction Partners</t>
+          <t>Echo Corp</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2013-08-02</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>2017-05-22</t>
-        </is>
-      </c>
+          <t>2010-05-25</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
-        <v>1007.7</v>
+        <v>905.7</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2022</v>
+        <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>100.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>122.2</v>
+        <v/>
       </c>
       <c r="K5" s="4" t="n">
-        <v>446.2</v>
+        <v>61</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.403</v>
+        <v>0.231</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Wei Ueno; Emma Vega</t>
+          <t>Elena Patel; Emma Yamamoto; Ahmed Kim</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -609,17 +605,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Meridian GmbH</t>
+          <t>Zenith Health</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -629,35 +625,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2012-03-15</t>
+          <t>2011-02-23</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2017-04-17</t>
+          <t>2018-03-16</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1315.3</v>
+        <v>1252.4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2774.9</v>
+        <v>3556.7</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>201.5</v>
+        <v>164.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>186.1</v>
+        <v>258.1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>252.2</v>
+        <v>295.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.784</v>
+        <v>0.606</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Yuki Patel; Sophie Yamamoto; Yuki Vega</t>
+          <t>Andrew Nakamura; Laura O'Brien</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -669,17 +665,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Yields Capital</t>
+          <t>Indigo Inc</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -689,35 +685,35 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010-03-15</t>
+          <t>2010-11-10</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2019-01-05</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>365.5</v>
+        <v>1259.2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>764.7</v>
+        <v>2123.2</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>55.5</v>
+        <v>316.4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>113.1</v>
+        <v>396.4</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>139.5</v>
+        <v>354.7</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.279</v>
+        <v>0.86</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Davis; Emma Anderson</t>
+          <t>Rachel Vega; Robert Rossi; David Ueno; Emma Williams</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -729,17 +725,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Radial Energy</t>
+          <t>Mosaic SA</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -749,35 +745,35 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2013-12-05</t>
+          <t>2013-11-28</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2017-10-31</t>
+          <t>2016-10-27</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>270.1</v>
+        <v>1745.7</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>392.8</v>
+        <v>3458.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>36.4</v>
+        <v>386.9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>68.8</v>
+        <v>865.3</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>151.9</v>
+        <v>1679.4</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.641</v>
+        <v>0.741</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Michael Xu; Wei Zhang</t>
+          <t>Ahmed Tanaka; Ravi O'Brien</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -789,55 +785,51 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Xenith Media</t>
+          <t>Gravity Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>2017-06-07</t>
-        </is>
-      </c>
+          <t>2011-06-12</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
-        <v>1665.1</v>
+        <v>248.6</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1592.8</v>
+        <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>295.2</v>
+        <v>43</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>707.5</v>
+        <v/>
       </c>
       <c r="K9" s="4" t="n">
-        <v>661.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.665</v>
+        <v>0.33</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Matthew Williams; Sarah Yamamoto; Rachel Hassan; Laura Nakamura</t>
+          <t>David Gupta; Laura Gupta; Michael Fischer</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -849,17 +841,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Tech</t>
+          <t>Gravity Inc</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -869,35 +861,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2011-08-04</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2019-12-29</t>
+          <t>2017-08-24</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>881.8</v>
+        <v>76.2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2537</v>
+        <v>192.4</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>172.2</v>
+        <v>17.2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>347.1</v>
+        <v>26.8</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>389.7</v>
+        <v>54.3</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.169</v>
+        <v>0.352</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Ravi O'Brien; Jennifer Anderson</t>
+          <t>James Tanaka; Jennifer Gupta</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -909,17 +901,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Group</t>
+          <t>Atlas SA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -929,35 +921,35 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2010-09-25</t>
+          <t>2013-03-27</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2014-11-09</t>
+          <t>2015-12-29</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>626.4</v>
+        <v>1985.4</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1602.3</v>
+        <v>3869.8</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>65.8</v>
+        <v>378.7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>121</v>
+        <v>346.3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>216.3</v>
+        <v>409.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.391</v>
+        <v>0.885</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Elena Brown; Olivia Yamamoto</t>
+          <t>Daniel Johnson; Daniel Fischer; Rachel Qureshi</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -969,7 +961,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Quanta Partners</t>
+          <t>Gravity Foods</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -979,45 +971,41 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2011-01-17</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>2014-04-09</t>
-        </is>
-      </c>
+          <t>2010-08-04</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>1059.5</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>97.2</v>
+        <v/>
       </c>
       <c r="I12" s="4" t="n">
-        <v>16.6</v>
+        <v>197.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>22.8</v>
+        <v/>
       </c>
       <c r="K12" s="4" t="n">
-        <v>52.4</v>
+        <v>789.1</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.745</v>
+        <v>0.2</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Mark Gupta; James Williams; Ravi Chen; Hannah Lopez</t>
+          <t>Ravi Lopez; Andrew Fischer; Andrew Tanaka; Daniel Fischer; Laura Ueno</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1029,17 +1017,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Drift Holdings</t>
+          <t>Wavelength Capital</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1049,117 +1037,113 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2010-07-04</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2017-05-08</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>643.3</v>
+        <v>627.8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2048.8</v>
+        <v>1039.9</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>174.6</v>
+        <v>133.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>349.6</v>
+        <v>213.5</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>573</v>
+        <v>559.3</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.434</v>
+        <v>0.517</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Olivia Rossi; Elena Williams; Emma Mueller</t>
+          <t>Sophie Rossi; Ahmed Davis</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Income</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Stratus Capital</t>
+          <t>Xenith Energy</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2012-10-26</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-19</t>
-        </is>
-      </c>
+          <t>2012-12-27</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
-        <v>1510.4</v>
+        <v>1510.8</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3560.9</v>
+        <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>288.8</v>
+        <v>185.3</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>705.1</v>
+        <v/>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1077.9</v>
+        <v>376.9</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.648</v>
+        <v>0.213</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Mark Kim; Matthew Davis; Amanda O'Brien; Daniel Ueno</t>
+          <t>Sophie Fischer; Matthew Kim; Thomas Fischer; Laura Schmidt; Christopher Xu</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Income</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Iris Logistics</t>
+          <t>Mosaic Ltd</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1169,57 +1153,57 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2013-11-27</t>
+          <t>2012-03-08</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2017-06-05</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>780.6</v>
+        <v>763.6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2410.5</v>
+        <v>1892.5</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>200.1</v>
+        <v>91.8</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>224.6</v>
+        <v>227.5</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>219.9</v>
+        <v>204.7</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.878</v>
+        <v>0.169</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Elena Kim; Ravi Vega; Andrew Chen</t>
+          <t>Yuki Kim; Olivia Patel; Sophie Evans; Jennifer Kim; James Rossi</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Income</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Apex Partners</t>
+          <t>Wavelength Labs</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1229,117 +1213,113 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2010-08-12</t>
+          <t>2012-01-08</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2018-09-24</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1900.3</v>
+        <v>763.6</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4845.1</v>
+        <v>1452.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>303.2</v>
+        <v>143.9</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>244.2</v>
+        <v>328.3</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>663.1</v>
+        <v>557.8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.51</v>
+        <v>0.613</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Vega; Thomas Hassan</t>
+          <t>Matthew Evans; Michael Ueno</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Income</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Junction GmbH</t>
+          <t>Indigo Networks</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2011-03-20</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>2017-03-25</t>
-        </is>
-      </c>
+          <t>2015-11-14</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
-        <v>1633.9</v>
+        <v>1119.8</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5308</v>
+        <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>370.6</v>
+        <v>229.9</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>405.1</v>
+        <v/>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1352.9</v>
+        <v>407.6</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.542</v>
+        <v>0.713</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Rachel Schmidt; Jessica Xu; Thomas Vega; Amanda Yamamoto; Sarah Johnson</t>
+          <t>Yuki Xu; Sophie Patel; Jessica Rossi; Michael Xu; Wei Chen</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Income</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Drift Ltd</t>
+          <t>Nova Bio</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1349,57 +1329,57 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2012-05-05</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>228.1</v>
+        <v>1305.3</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>239.2</v>
+        <v>1851.2</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>60.3</v>
+        <v>326.6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>52.9</v>
+        <v>780.7</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>123.9</v>
+        <v>899.1</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.166</v>
+        <v>0.287</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Sophie Schmidt; Jessica Rossi</t>
+          <t>Michael Kim; Hannah Lopez; Robert Brown; Priya Chen; Ravi O'Brien</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Income</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Gravity Corp</t>
+          <t>Helix Networks</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1409,57 +1389,57 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2012-02-26</t>
+          <t>2012-02-01</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2017-05-16</t>
+          <t>2017-12-12</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1036.8</v>
+        <v>1837.2</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3292.9</v>
+        <v>1589.8</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>94</v>
+        <v>211.1</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>117.8</v>
+        <v>483.4</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>86.7</v>
+        <v>682.7</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Yuki Mueller; Mark Ueno; Elena Zhang; Wei Xu; Amanda Johnson</t>
+          <t>Jessica Brown; Jessica Schmidt</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Income</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Glacier Bio</t>
+          <t>Bloom GmbH</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1469,57 +1449,57 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2010-01-02</t>
+          <t>2013-05-13</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2018-01-26</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1647.5</v>
+        <v>1692.6</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4579.1</v>
+        <v>1686.5</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>420</v>
+        <v>458.6</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>353.7</v>
+        <v>868</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1477.4</v>
+        <v>1215.4</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.421</v>
+        <v>0.385</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Thomas O'Brien; Ravi Brown; Olivia Yamamoto; James Vega; Priya Rossi</t>
+          <t>Mark Mueller; Yuki Fischer; Sarah Lopez; Daniel Vega; Andrew Mueller</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Income</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Partners</t>
+          <t>Vertex Inc</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1529,35 +1509,35 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2015-11-26</t>
+          <t>2015-07-24</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>680.2</v>
+        <v>1005.3</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>983.8</v>
+        <v>2554.5</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>78.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>132.5</v>
+        <v>223.2</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>183.8</v>
+        <v>212</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.761</v>
+        <v>0.837</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Michael Schmidt; Matthew Evans; Ravi Hassan; Robert Chen</t>
+          <t>James Johnson; Amanda Davis; Sarah Qureshi; Amanda Brown; Elena Fischer</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1569,17 +1549,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Kepler Industries</t>
+          <t>Lumen Energy</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1589,35 +1569,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2013-07-10</t>
+          <t>2012-03-01</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2018-08-03</t>
+          <t>2016-05-15</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>309.1</v>
+        <v>936.9</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>435.1</v>
+        <v>2449</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>50.5</v>
+        <v>81.3</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>110.9</v>
+        <v>139.6</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>307.9</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.896</v>
+        <v>0.643</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Hassan; Jessica Anderson; Christopher Zhang; Yuki Zhang; Jennifer Ueno</t>
+          <t>James Brown; Michael Ivanov; Amanda Tanaka; Wei Tanaka; Sophie Kim</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -1629,51 +1609,55 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Media</t>
+          <t>Halo Corp</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2013-09-17</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+          <t>2013-06-03</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>2019-06-17</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n">
-        <v>758.6</v>
+        <v>1151.9</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v/>
+        <v>2696</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>159.8</v>
+        <v>223.9</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v/>
+        <v>524.1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>446.1</v>
+        <v>616.8</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.754</v>
+        <v>0.785</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Schmidt; Amanda Tanaka; Daniel Hassan</t>
+          <t>Michael Gupta; Christopher Anderson; Sarah Ivanov; Matthew Xu</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -1685,7 +1669,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Iris Logic</t>
+          <t>Halo AG</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1695,7 +1679,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1705,57 +1689,57 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2012-08-09</t>
+          <t>2015-02-22</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2021-12-11</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1417.5</v>
+        <v>1800.6</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1813.6</v>
+        <v>3991.1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>373.1</v>
+        <v>220</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>590.3</v>
+        <v>293.4</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1251.9</v>
+        <v>845.4</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.672</v>
+        <v>0.2</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Michael Qureshi; Ravi Lopez; Amanda Johnson; Robert Patel; Hannah Brown</t>
+          <t>Ravi Gupta; Michael Vega; Sarah Hassan</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Stability</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Junction Networks</t>
+          <t>Cipher Labs</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1765,57 +1749,57 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2015-10-24</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2018-11-26</t>
+          <t>2019-07-31</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1440</v>
+        <v>335.5</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3501.1</v>
+        <v>635.9</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>157.3</v>
+        <v>92.3</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>171.3</v>
+        <v>162.6</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>499.7</v>
+        <v>103.4</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.628</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Emma Vega; Priya Nakamura; Laura Yamamoto</t>
+          <t>Sophie Qureshi; Yuki Hassan; Rachel Mueller; Rachel Yamamoto</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Stability</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Beacon Holdings</t>
+          <t>Helix Holdings</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1825,57 +1809,57 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2014-07-26</t>
+          <t>2015-09-14</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2020-09-13</t>
+          <t>2019-10-28</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>491.3</v>
+        <v>1885.4</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>803.2</v>
+        <v>2224.3</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>70.2</v>
+        <v>194.8</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>109.5</v>
+        <v>389.7</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>154</v>
+        <v>694.7</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.708</v>
+        <v>0.589</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>David Chen; Sophie Yamamoto</t>
+          <t>Olivia Tanaka; Hannah Johnson; Mark Hassan; Rachel Tanaka</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Stability</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Apex Industries</t>
+          <t>Zenith Capital</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1885,57 +1869,57 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2013-03-08</t>
+          <t>2015-02-11</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>218</v>
+        <v>294.4</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>275</v>
+        <v>616.8</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>59</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.868</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Andrew Williams; Rachel Hassan; Hannah Mueller</t>
+          <t>Yuki Johnson; Jessica Qureshi; Robert Vega; Ahmed Williams</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Stability</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Polaris Inc</t>
+          <t>Nova Materials</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1945,43 +1929,43 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2013-08-16</t>
+          <t>2015-07-18</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
-        <v>402.7</v>
+        <v>1952.2</v>
       </c>
       <c r="H28" s="4" t="n">
         <v/>
       </c>
       <c r="I28" s="4" t="n">
-        <v>39.3</v>
+        <v>430.8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v/>
       </c>
       <c r="K28" s="4" t="n">
-        <v>138.1</v>
+        <v>977.4</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.984</v>
+        <v>0.826</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Olivia Zhang; Olivia Lopez; Rachel Williams; Jennifer Davis</t>
+          <t>Jessica Gupta; Sarah Davis</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Stability</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Drift Tech</t>
+          <t>Ember Media</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1991,123 +1975,123 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>2019-09-07</t>
-        </is>
-      </c>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
-        <v>582.2</v>
+        <v>407.9</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1010.4</v>
+        <v/>
       </c>
       <c r="I29" s="4" t="n">
-        <v>105.8</v>
+        <v>103.6</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>167.1</v>
+        <v/>
       </c>
       <c r="K29" s="4" t="n">
-        <v>222.8</v>
+        <v>275.3</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.346</v>
+        <v>0.475</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Daniel Xu; Robert Ivanov</t>
+          <t>Ravi Williams; Sophie Gupta; Rachel Xu; Hannah Patel; James Ivanov</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Stability</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Lumen Health</t>
+          <t>Ember SA</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2012-03-17</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>2016-09-11</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n">
-        <v>291.7</v>
+        <v>1661.4</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v/>
+        <v>1784.6</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>42.6</v>
+        <v>227.5</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v/>
+        <v>274</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>56.7</v>
+        <v>597.2</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.255</v>
+        <v>0.573</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Ravi Ueno; Jennifer Vega; Yuki Schmidt</t>
+          <t>James Williams; Mark Nakamura; Yuki Vega; Daniel Patel; Emma Ueno</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Stability</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Orion Pharma</t>
+          <t>Gravity Logic</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2117,47 +2101,47 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2013-03-18</t>
+          <t>2016-01-03</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>925.2</v>
+        <v>621.7</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1756.8</v>
+        <v>1665.7</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>253.1</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>209</v>
+        <v>190.2</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>839.2</v>
+        <v>146.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.198</v>
+        <v>0.766</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>David Fischer; Andrew Nakamura; Priya Davis</t>
+          <t>Jessica Tanaka; Sarah Nakamura</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Stability</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Atlas Solutions</t>
+          <t>Orion Systems</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2167,7 +2151,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2177,35 +2161,35 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2015-11-11</t>
+          <t>2014-03-11</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2020-01-25</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1243.1</v>
+        <v>791.5</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1482.9</v>
+        <v>1825.2</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>217.4</v>
+        <v>79.7</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>186</v>
+        <v>131.7</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>111</v>
+        <v>240.4</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.277</v>
+        <v>0.524</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Wei Nakamura; Jennifer O'Brien; Sophie Williams; Jennifer Fischer; Elena Zhang</t>
+          <t>Elena Lopez; Jennifer Vega</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2217,17 +2201,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Indigo Inc</t>
+          <t>Drift Group</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2237,35 +2221,35 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2022-12-13</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>484.8</v>
+        <v>515.5</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1435</v>
+        <v>1175.6</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>64.5</v>
+        <v>108.3</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>107.6</v>
+        <v>121.8</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>279.8</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.627</v>
+        <v>0.896</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Thomas Davis; David Kim; Elena Rossi; Ahmed Hassan; Sophie Anderson</t>
+          <t>Jessica Kim; Ahmed Vega</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -2277,12 +2261,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Orion Solutions</t>
+          <t>Quanta AG</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2292,36 +2276,40 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2016-09-11</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr"/>
+          <t>2016-08-05</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n">
-        <v>1214.9</v>
+        <v>1186.8</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v/>
+        <v>2184.7</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>110.6</v>
+        <v>294.8</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v/>
+        <v>283.1</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>362.7</v>
+        <v>653.6</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.761</v>
+        <v>0.758</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Christopher O'Brien; Sophie Kim; Mark O'Brien</t>
+          <t>Thomas Mueller; Amanda Tanaka</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2333,17 +2321,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Cobalt Pharma</t>
+          <t>Kepler Materials</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2353,35 +2341,35 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
+          <t>2014-12-08</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2018-04-04</t>
+          <t>2018-01-02</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1577.5</v>
+        <v>1361.6</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2572.4</v>
+        <v>4117.2</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>430.9</v>
+        <v>260.3</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1071.4</v>
+        <v>570.8</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1300.8</v>
+        <v>590.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.297</v>
+        <v>0.913</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Christopher Ueno; Elena Hassan; Ravi Lopez; Robert Ivanov; Daniel Evans</t>
+          <t>Sophie Mueller; Robert Anderson</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -2393,17 +2381,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Bloom SA</t>
+          <t>Nova Inc</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2413,35 +2401,35 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2014-04-23</t>
+          <t>2015-01-24</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2017-03-12</t>
+          <t>2022-02-06</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1690.1</v>
+        <v>1544.1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>5068.4</v>
+        <v>1485.6</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>178.5</v>
+        <v>319.3</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>217.2</v>
+        <v>532.7</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>603.9</v>
+        <v>1161.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.162</v>
+        <v>0.505</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Thomas Evans; Daniel Yamamoto; David Brown; Daniel Zhang; Christopher Anderson</t>
+          <t>Ravi Johnson; Olivia Mueller; Wei Johnson; Jennifer Vega; Sarah Gupta</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -2453,55 +2441,51 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Halo Networks</t>
+          <t>Tessera Energy</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2015-02-17</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>2020-02-01</t>
-        </is>
-      </c>
+          <t>2016-04-20</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
-        <v>1079.5</v>
+        <v>1539.9</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2493.2</v>
+        <v/>
       </c>
       <c r="I37" s="4" t="n">
-        <v>279.3</v>
+        <v>232</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>273.5</v>
+        <v/>
       </c>
       <c r="K37" s="4" t="n">
-        <v>770</v>
+        <v>661.4</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.671</v>
+        <v>0.589</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Mark Hassan; Michael Davis; Sarah Chen</t>
+          <t>Emma Kim; Robert Nakamura; Amanda Schmidt; Laura Yamamoto</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2513,17 +2497,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Radial Bio</t>
+          <t>Helix Capital</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2533,35 +2517,35 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
+          <t>2016-07-20</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1186.1</v>
+        <v>1539.9</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2742.5</v>
+        <v>4890.6</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>218.1</v>
+        <v>229.8</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>486.7</v>
+        <v>301.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>889.3</v>
+        <v>470</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.314</v>
+        <v>0.443</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Priya Ueno; Priya Rossi; James Brown; Mark Ueno</t>
+          <t>Elena Ueno; Wei Anderson</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -2573,51 +2557,55 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Yields Tech</t>
+          <t>Helix Tech</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2014-08-10</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
+          <t>2017-10-17</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-08</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n">
-        <v>1764.6</v>
+        <v>723.7</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v/>
+        <v>2474.8</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>280.3</v>
+        <v>134.2</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v/>
+        <v>177.3</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>211.3</v>
+        <v>515.6</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.468</v>
+        <v>0.698</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Yuki Gupta; Olivia Qureshi; Emma Ivanov</t>
+          <t>Andrew Gupta; Ahmed Hassan; Rachel Lopez; Sophie Evans</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -2629,7 +2617,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Meridian Systems</t>
+          <t>Atlas Pharma</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2639,41 +2627,45 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2014-12-13</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
+          <t>2014-08-02</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n">
-        <v>210.8</v>
+        <v>642.8</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v/>
+        <v>1391.6</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>57.7</v>
+        <v>132.3</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v/>
+        <v>279</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>240.6</v>
+        <v>304.6</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.845</v>
+        <v>0.704</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Rachel Anderson; Sarah Lopez</t>
+          <t>Olivia Brown; Sophie Vega; Laura Kim; Andrew Williams; Wei Evans</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -2685,17 +2677,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Junction Energy</t>
+          <t>Tessera Foods</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2705,35 +2697,35 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2017-05-20</t>
+          <t>2016-03-08</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2022-07-04</t>
+          <t>2020-04-03</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>504.1</v>
+        <v>1641.3</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>621.5</v>
+        <v>5424.2</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>63.2</v>
+        <v>344.7</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>100.3</v>
+        <v>643.3</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>247.9</v>
+        <v>624</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.423</v>
+        <v>0.822</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Robert Xu; Ravi Anderson; Jennifer Johnson; Mark Nakamura</t>
+          <t>Laura Patel; Amanda Qureshi; Christopher Nakamura; Laura Tanaka</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -2745,17 +2737,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Umbra Logic</t>
+          <t>Zenith Bio</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2765,35 +2757,35 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2016-08-20</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1067.8</v>
+        <v>539.1</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>3191</v>
+        <v>1214.8</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>294.1</v>
+        <v>106.3</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>398.2</v>
+        <v>142</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>443.7</v>
+        <v>120.1</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.709</v>
+        <v>0.395</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Christopher Tanaka; Mark Fischer</t>
+          <t>Jessica Rossi; Sophie Zhang; Yuki Yamamoto; Sophie Chen</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -2805,7 +2797,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Polaris Energy</t>
+          <t>Indigo Industries</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2815,7 +2807,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2825,35 +2817,35 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2017-10-17</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>772</v>
+        <v>1219.4</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>876.4</v>
+        <v>1914.8</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>146.1</v>
+        <v>292.7</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>332</v>
+        <v>517</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>162.4</v>
+        <v>909.5</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.917</v>
+        <v>0.355</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Elena Vega; David Lopez; Christopher Brown; Daniel Lopez; Daniel Nakamura</t>
+          <t>Olivia Qureshi; Olivia Yamamoto; Olivia Tanaka</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -2865,17 +2857,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Nova Tech</t>
+          <t>Stratus Solutions</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2885,35 +2877,35 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2017-08-18</t>
+          <t>2016-07-27</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1232.7</v>
+        <v>148.8</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>3866.2</v>
+        <v>469</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>254.8</v>
+        <v>13.5</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>240.5</v>
+        <v>15</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>837.9</v>
+        <v>41.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.451</v>
+        <v>0.314</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Olivia Davis; Yuki Rossi</t>
+          <t>Wei Evans; Ahmed O'Brien; Daniel Qureshi</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -2925,55 +2917,51 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Orion Health</t>
+          <t>Gravity Labs</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2015-04-05</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>2019-03-16</t>
-        </is>
-      </c>
+          <t>2016-12-05</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
-        <v>1161.3</v>
+        <v>1010.4</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>3773.8</v>
+        <v/>
       </c>
       <c r="I45" s="4" t="n">
-        <v>315.8</v>
+        <v>255.9</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>427.9</v>
+        <v/>
       </c>
       <c r="K45" s="4" t="n">
-        <v>190.3</v>
+        <v>1004.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>0.41</v>
+        <v>0.859</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Mark Chen; Hannah Chen; David Davis; Hannah Davis</t>
+          <t>Rachel Zhang; Sarah Xu; Yuki Vega</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -2985,17 +2973,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Bloom Media</t>
+          <t>Lattice Labs</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3005,35 +2993,35 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2016-12-16</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>635.2</v>
+        <v>514.4</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>2179.4</v>
+        <v>371.1</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>153.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>202</v>
+        <v>167.7</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>206.4</v>
+        <v>181.1</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.887</v>
+        <v>0.217</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Thomas Schmidt; Sarah Ivanov; David Mueller; Sophie Johnson</t>
+          <t>Mark Evans; Sophie Chen</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -3045,17 +3033,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Umbra Ltd</t>
+          <t>Glacier Tech</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3065,35 +3053,35 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2017-09-23</t>
+          <t>2016-08-25</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2019-07-12</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1544.6</v>
+        <v>284.1</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>5012.2</v>
+        <v>689.8</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>178.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>163.4</v>
+        <v>112.6</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>326.5</v>
+        <v>156.1</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.972</v>
+        <v>0.335</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Ravi Zhang; Priya Fischer; Olivia Ueno</t>
+          <t>Ravi Vega; Rachel Williams; James Qureshi; Christopher Fischer; Ahmed Ivanov</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -3105,17 +3093,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Nova Inc</t>
+          <t>Junction AG</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3125,35 +3113,35 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2014-01-05</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2020-12-06</t>
+          <t>2019-05-05</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1662.2</v>
+        <v>1171.5</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>4465.9</v>
+        <v>3891.7</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>361.6</v>
+        <v>307.2</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>571.6</v>
+        <v>466.3</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>582</v>
+        <v>1177.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.912</v>
+        <v>0.336</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Hannah Anderson; Christopher Yamamoto; Robert Evans</t>
+          <t>Andrew Ivanov; Jessica Mueller; Christopher Qureshi; Sophie Qureshi</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -3165,17 +3153,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Helix Dynamics</t>
+          <t>Atlas Energy</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3185,35 +3173,35 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2017-01-20</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>1487.4</v>
+        <v>1412.4</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1819.2</v>
+        <v>3485.1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>379.7</v>
+        <v>136.7</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>353.3</v>
+        <v>321.5</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1309.5</v>
+        <v>281.4</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>0.429</v>
+        <v>0.973</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Elena Johnson; Elena Evans; Elena Vega; Rachel Johnson</t>
+          <t>Jessica Williams; Ahmed Kim</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -3225,17 +3213,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Bloom Inc</t>
+          <t>Drift Foods</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3245,35 +3233,35 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2019-04-28</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>673.1</v>
+        <v>556.1</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>642.1</v>
+        <v>1750.3</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>157.9</v>
+        <v>74</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>262.5</v>
+        <v>73.8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>604.3</v>
+        <v>128.3</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.19</v>
+        <v>0.727</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Thomas Qureshi; Laura Chen; Sarah Tanaka</t>
+          <t>Emma Hassan; Andrew Evans; Robert Ivanov; Amanda Evans</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -3285,12 +3273,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Orion Inc</t>
+          <t>Cobalt Corp</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -3305,35 +3293,35 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-09-05</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2022-03-24</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1976.8</v>
+        <v>1823.4</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>4456</v>
+        <v>1808.2</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>452.8</v>
+        <v>410.1</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>920.3</v>
+        <v>1007.9</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>549.5</v>
+        <v>1491</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>0.926</v>
+        <v>0.174</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>Mark Vega; Hannah Yamamoto; Mark Patel; Emma Davis</t>
+          <t>Matthew Ivanov; Christopher Qureshi</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -3345,17 +3333,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Atlas Group</t>
+          <t>Stratus Health</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3365,35 +3353,35 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2018-11-04</t>
+          <t>2018-05-27</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>403.5</v>
+        <v>1843.7</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>836.7</v>
+        <v>3857.9</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>219.3</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>198.7</v>
+        <v>415</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>212</v>
+        <v>882</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.333</v>
+        <v>0.991</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Yuki Fischer; Sophie Evans; Ravi Patel</t>
+          <t>Matthew Anderson; Priya Rossi</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -3405,17 +3393,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Yields Group</t>
+          <t>Forge Logic</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3425,35 +3413,35 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2017-07-24</t>
+          <t>2018-04-10</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1475.9</v>
+        <v>1775.1</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1760.6</v>
+        <v>5491.1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>248.2</v>
+        <v>199.3</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>442.4</v>
+        <v>197.2</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>377.4</v>
+        <v>683.5</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0.3</v>
+        <v>0.428</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Jessica Patel; Rachel Zhang</t>
+          <t>Ravi Yamamoto; Elena Anderson; Sarah Rossi</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -3465,17 +3453,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Halo Labs</t>
+          <t>Drift Solutions</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3485,35 +3473,35 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-02-25</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2019-12-22</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>1799.9</v>
+        <v>1095.9</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>3914.4</v>
+        <v>999.9</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>430.2</v>
+        <v>138.4</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>659.5</v>
+        <v>125.6</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>261.7</v>
+        <v>104.7</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.413</v>
+        <v>0.158</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Anderson; Andrew Zhang</t>
+          <t>Mark Tanaka; Robert Qureshi; Rachel Ivanov; Elena Gupta; Ravi Johnson</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -3525,51 +3513,55 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Bloom Tech</t>
+          <t>Junction Networks</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
+          <t>2018-03-24</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n">
-        <v>529.1</v>
+        <v>773.6</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v/>
+        <v>595.7</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>145.8</v>
+        <v>210.7</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v/>
+        <v>264.5</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>238.2</v>
+        <v>498.7</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.644</v>
+        <v>0.556</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>David Nakamura; Andrew Williams; Hannah Evans; Priya Ivanov; James Rossi</t>
+          <t>Laura Qureshi; Amanda Mueller</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -3581,17 +3573,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Orion AG</t>
+          <t>Tessera Bio</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3601,35 +3593,35 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2018-03-02</t>
+          <t>2018-03-03</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1988.1</v>
+        <v>1418.9</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>5967.7</v>
+        <v>2184.5</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>247.7</v>
+        <v>140.3</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>483.6</v>
+        <v>219.3</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>650.4</v>
+        <v>607.6</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.582</v>
+        <v>0.427</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Robert Williams; Christopher Gupta; Andrew Hassan; Hannah Patel</t>
+          <t>Daniel Brown; Amanda Mueller; Matthew Yamamoto; Jessica Nakamura; Rachel Ivanov</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -3641,17 +3633,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Junction Systems</t>
+          <t>Quanta Dynamics</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3661,35 +3653,35 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2017-02-23</t>
+          <t>2019-07-10</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>1182</v>
+        <v>1538.8</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>2446.4</v>
+        <v>4258.6</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>165.5</v>
+        <v>374.8</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>395.7</v>
+        <v>657.5</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>1168.8</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0.748</v>
+        <v>0.987</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Lopez; Jessica Johnson; Olivia Tanaka; Elena Tanaka</t>
+          <t>Thomas Brown; Mark Yamamoto</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -3701,17 +3693,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Lattice Holdings</t>
+          <t>Junction Corp</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3721,35 +3713,35 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2017-05-28</t>
+          <t>2016-01-07</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2020-04-26</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1999.1</v>
+        <v>935.1</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>5913</v>
+        <v>2391.1</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>436.7</v>
+        <v>233.6</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>1038.6</v>
+        <v>443</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>219.8</v>
+        <v>195.8</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.789</v>
+        <v>0.866</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Elena Brown; Daniel Brown; Andrew Yamamoto; Emma Anderson</t>
+          <t>James Tanaka; Wei Nakamura</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -3761,17 +3753,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Fathom Logic</t>
+          <t>Xenith Media</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3781,35 +3773,35 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>1045.9</v>
+        <v>1681</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2399.4</v>
+        <v>3122.9</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>109.7</v>
+        <v>224.1</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>204.2</v>
+        <v>464.2</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>343.1</v>
+        <v>516.6</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>0.985</v>
+        <v>0.276</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>Sarah Lopez; Andrew Kim</t>
+          <t>David Rossi; Matthew Hassan</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -3821,17 +3813,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Atlas Partners</t>
+          <t>Meridian Industries</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3841,35 +3833,35 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2016-08-28</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>1350.1</v>
+        <v>1183.3</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1935.2</v>
+        <v>3228.5</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>279</v>
+        <v>284.1</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>688.3</v>
+        <v>336.8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>985.9</v>
+        <v>681.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.76</v>
+        <v>0.746</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Ravi Fischer; Ravi Tanaka; Robert Evans; Ravi Xu</t>
+          <t>Sophie Zhang; Hannah Rossi</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -3881,17 +3873,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Cobalt Bio</t>
+          <t>Polaris Systems</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3901,35 +3893,35 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2018-12-05</t>
+          <t>2018-03-10</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>374.3</v>
+        <v>1667</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>750</v>
+        <v>4133</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>60.8</v>
+        <v>428.5</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>127.5</v>
+        <v>522.1</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>69.90000000000001</v>
+        <v>508.3</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>0.162</v>
+        <v>0.746</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>Jessica Zhang; David Nakamura</t>
+          <t>Jessica Zhang; Jessica Anderson; Sarah Qureshi; Olivia Zhang</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -3941,55 +3933,51 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Iris Holdings</t>
+          <t>Indigo Bio</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2018-05-06</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
-        <v>571.1</v>
+        <v>1766.1</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1035.1</v>
+        <v/>
       </c>
       <c r="I62" s="4" t="n">
-        <v>117.2</v>
+        <v>217.5</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>129.7</v>
+        <v/>
       </c>
       <c r="K62" s="4" t="n">
-        <v>512.6</v>
+        <v>208.9</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.782</v>
+        <v>0.648</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Mark Xu; Sarah Johnson; Yuki Williams</t>
+          <t>Elena Brown; Jessica Yamamoto; Thomas Qureshi; Elena Zhang; Emma Schmidt</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
